--- a/artfynd/A 57460-2022 artfynd.xlsx
+++ b/artfynd/A 57460-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57460-2022 artfynd.xlsx
+++ b/artfynd/A 57460-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>158467</v>
+        <v>157786</v>
       </c>
       <c r="B2" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>STJÄRNVIK, Ög</t>
+          <t>Butbacken, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550348.5538215549</v>
+        <v>550349</v>
       </c>
       <c r="R2" t="n">
-        <v>6507801.629695883</v>
+        <v>6507802</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-12-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-12-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På minst 3 träd i sluttning med grova ekar samt ask, lönn, tall o asp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,11 +762,10 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -784,23 +773,14 @@
           <t>Jens Johannesson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>414172</v>
+        <v>87326642</v>
       </c>
       <c r="B3" t="n">
-        <v>73592</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1458</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grå skärelav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dendrographa decolorans</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>STJÄRNVIK, Ög</t>
+          <t>Stjärnviksområdet, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550348.5538215549</v>
+        <v>550319</v>
       </c>
       <c r="R3" t="n">
-        <v>6507801.629695883</v>
+        <v>6507785</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,73 +859,63 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4956560</v>
+        <v>87326539</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Butbacken, Ög</t>
+          <t>Stjärnviksområdet, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550348.5538215549</v>
+        <v>550512</v>
       </c>
       <c r="R4" t="n">
-        <v>6507801.629695883</v>
+        <v>6507712</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1996-12-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1996-12-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ekskog</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,65 +959,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>182570</v>
+        <v>87326482</v>
       </c>
       <c r="B5" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1114</v>
+        <v>826</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Lundvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Hygrophorus nemoreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>(Pers.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Butbacken, Ög</t>
+          <t>Stjärnviksområdet, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550348.5538215549</v>
+        <v>550524</v>
       </c>
       <c r="R5" t="n">
-        <v>6507801.629695883</v>
+        <v>6507722</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,27 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1996-12-10</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1996-12-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 1,5 kvdm.</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1056,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72231323</v>
+        <v>182570</v>
       </c>
       <c r="B6" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,53 +1079,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1897</v>
+        <v>1114</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stjärnvik herrgård 1,02 km O, Ög</t>
+          <t>Butbacken, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550404.4963781586</v>
+        <v>550349</v>
       </c>
       <c r="R6" t="n">
-        <v>6507742.601959336</v>
+        <v>6507802</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,27 +1133,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-12-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-12-10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>vit variant</t>
+          <t>Ca 1,5 kvdm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,61 +1152,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>skogsstig</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britt-Marie Ericson</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britt-Marie Ericson, Ingegerd Hedbäck</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87326642</v>
+        <v>87326649</v>
       </c>
       <c r="B7" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>311</v>
+        <v>1114</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550319.0969816936</v>
+        <v>550140</v>
       </c>
       <c r="R7" t="n">
-        <v>6507785.140697533</v>
+        <v>6507872</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,19 +1238,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,37 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87326648</v>
+        <v>87326650</v>
       </c>
       <c r="B8" t="n">
-        <v>86011</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4037</v>
+        <v>1114</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bolmörtsskivling</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Entoloma sinuatum</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bull.) P.Kumm.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550139.9299366438</v>
+        <v>550302</v>
       </c>
       <c r="R8" t="n">
-        <v>6507873.751265476</v>
+        <v>6507789</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,28 +1335,17 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1507,37 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87326576</v>
+        <v>87326651</v>
       </c>
       <c r="B9" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2779</v>
+        <v>1114</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550349.2358765485</v>
+        <v>550322</v>
       </c>
       <c r="R9" t="n">
-        <v>6507789.168372293</v>
+        <v>6507789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,19 +1432,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87326699</v>
+        <v>87326652</v>
       </c>
       <c r="B10" t="n">
-        <v>4964</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101608</v>
+        <v>1114</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550511.0949798281</v>
+        <v>550357</v>
       </c>
       <c r="R10" t="n">
-        <v>6507751.260983545</v>
+        <v>6507774</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,19 +1529,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87326458</v>
+        <v>87326404</v>
       </c>
       <c r="B11" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1460</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550153.2265298847</v>
+        <v>550504</v>
       </c>
       <c r="R11" t="n">
-        <v>6507892.108143876</v>
+        <v>6507763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,19 +1626,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,53 +1655,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87326649</v>
+        <v>414169</v>
       </c>
       <c r="B12" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1114</v>
+        <v>1458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Grå skärelav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Dendrographa decolorans</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>(Turner &amp; Borrer ex Sm.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stjärnviksområdet, Ög</t>
+          <t>Butbacken, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550139.9500538964</v>
+        <v>550349</v>
       </c>
       <c r="R12" t="n">
-        <v>6507872.1927882</v>
+        <v>6507802</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1913,22 +1720,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-12-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1996-12-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2-3 kvdm på nordsidan av lutande ek intill grusväg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,49 +1745,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87326619</v>
+        <v>87326458</v>
       </c>
       <c r="B13" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>1460</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1995,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550158.9513080629</v>
+        <v>550153</v>
       </c>
       <c r="R13" t="n">
-        <v>6507892.182065185</v>
+        <v>6507892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,19 +1825,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,15 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87326650</v>
+        <v>72231323</v>
       </c>
       <c r="B14" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,34 +1865,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1114</v>
+        <v>1897</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stjärnviksområdet, Ög</t>
+          <t>Stjärnvik herrgård 1,02 km O, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550301.8683514289</v>
+        <v>550404</v>
       </c>
       <c r="R14" t="n">
-        <v>6507789.074284976</v>
+        <v>6507743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,22 +1935,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>vit variant</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,33 +1954,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>skogsstig</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Britt-Marie Ericson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Britt-Marie Ericson, Ingegerd Hedbäck</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87326652</v>
+        <v>79740503</v>
       </c>
       <c r="B15" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,34 +1989,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1114</v>
+        <v>1897</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stjärnviksområdet, Ög</t>
+          <t>Butbro, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550357.2379084887</v>
+        <v>550235</v>
       </c>
       <c r="R15" t="n">
-        <v>6507774.203932215</v>
+        <v>6507787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,22 +2043,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ytterslänt flera stycken</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,31 +2064,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>87326651</v>
+        <v>79740504</v>
       </c>
       <c r="B16" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,34 +2096,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1114</v>
+        <v>1897</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stjärnviksområdet, Ög</t>
+          <t>Butbro, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550322.1725641167</v>
+        <v>550197</v>
       </c>
       <c r="R16" t="n">
-        <v>6507788.817678116</v>
+        <v>6507812</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,22 +2150,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ytterslänt flera stycken</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,66 +2171,66 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87326577</v>
+        <v>79740505</v>
       </c>
       <c r="B17" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2779</v>
+        <v>1897</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stjärnviksområdet, Ög</t>
+          <t>Butbro, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550361.888284397</v>
+        <v>550182</v>
       </c>
       <c r="R17" t="n">
-        <v>6507776.862185725</v>
+        <v>6507821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,22 +2257,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ytterslänt flera stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,66 +2278,66 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87326481</v>
+        <v>79740506</v>
       </c>
       <c r="B18" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4786</v>
+        <v>1897</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius volemus</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stjärnviksområdet, Ög</t>
+          <t>Butbro, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550158.2458483466</v>
+        <v>550174</v>
       </c>
       <c r="R18" t="n">
-        <v>6507866.194043847</v>
+        <v>6507827</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2585,22 +2364,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ytterslänt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,53 +2385,53 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>87326412</v>
+        <v>87326496</v>
       </c>
       <c r="B19" t="n">
-        <v>86136</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4379</v>
+        <v>1897</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2667,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550438.8204325712</v>
+        <v>550263</v>
       </c>
       <c r="R19" t="n">
-        <v>6507785.134664397</v>
+        <v>6507807</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,19 +2474,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,37 +2503,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>87326575</v>
+        <v>87326497</v>
       </c>
       <c r="B20" t="n">
-        <v>92939</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2779</v>
+        <v>1897</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2779,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550148.1026681968</v>
+        <v>550284</v>
       </c>
       <c r="R20" t="n">
-        <v>6507885.807066351</v>
+        <v>6507798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2812,19 +2571,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,12 +2603,7 @@
         <v>87326532</v>
       </c>
       <c r="B21" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2891,10 +2635,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550159.9586345962</v>
+        <v>550160</v>
       </c>
       <c r="R21" t="n">
-        <v>6507894.792954844</v>
+        <v>6507895</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,19 +2668,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,37 +2697,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>87326404</v>
+        <v>87326619</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3003,10 +2732,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550504.1737332847</v>
+        <v>550159</v>
       </c>
       <c r="R22" t="n">
-        <v>6507763.121696807</v>
+        <v>6507892</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3036,19 +2765,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,12 +2797,7 @@
         <v>87326620</v>
       </c>
       <c r="B23" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,10 +2829,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550429.972801201</v>
+        <v>550430</v>
       </c>
       <c r="R23" t="n">
-        <v>6507785.019789625</v>
+        <v>6507785</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,19 +2862,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,37 +2891,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>87326657</v>
+        <v>87326628</v>
       </c>
       <c r="B24" t="n">
-        <v>101219</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221978</v>
+        <v>2671</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypericum montanum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3227,10 +2926,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550452.8118247465</v>
+        <v>550125</v>
       </c>
       <c r="R24" t="n">
-        <v>6507789.992689929</v>
+        <v>6507936</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3260,19 +2959,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,37 +2988,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87326497</v>
+        <v>87326575</v>
       </c>
       <c r="B25" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1897</v>
+        <v>2779</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3339,10 +3023,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550284.0520597959</v>
+        <v>550148</v>
       </c>
       <c r="R25" t="n">
-        <v>6507798.196235257</v>
+        <v>6507886</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3372,19 +3056,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,37 +3085,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87326705</v>
+        <v>87326576</v>
       </c>
       <c r="B26" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>2779</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3451,10 +3120,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550346.025654257</v>
+        <v>550349</v>
       </c>
       <c r="R26" t="n">
-        <v>6507795.881440583</v>
+        <v>6507789</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3484,19 +3153,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,37 +3182,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87326496</v>
+        <v>87326577</v>
       </c>
       <c r="B27" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1897</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3217,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550263.1199001668</v>
+        <v>550362</v>
       </c>
       <c r="R27" t="n">
-        <v>6507806.758335446</v>
+        <v>6507777</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,19 +3250,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,37 +3279,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87326555</v>
+        <v>87326590</v>
       </c>
       <c r="B28" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221317</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3675,10 +3314,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550262.072286344</v>
+        <v>550133</v>
       </c>
       <c r="R28" t="n">
-        <v>6507807.26436807</v>
+        <v>6507933</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3708,19 +3347,9 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2020-08-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,37 +3376,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87326710</v>
+        <v>87326648</v>
       </c>
       <c r="B29" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>90312</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223246</v>
+        <v>4037</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Bolmörtsskivling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Entoloma sinuatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Bull.) P.Kumm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3787,10 +3411,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550346.0391207855</v>
+        <v>550140</v>
       </c>
       <c r="R29" t="n">
-        <v>6507794.842434786</v>
+        <v>6507874</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3820,27 +3444,18 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3859,15 +3474,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96634221</v>
+        <v>87326412</v>
       </c>
       <c r="B30" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3875,39 +3485,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>4379</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Stjärnviksområdet, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550355.1493727682</v>
+        <v>550439</v>
       </c>
       <c r="R30" t="n">
-        <v>6507774.696450488</v>
+        <v>6507785</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3931,22 +3539,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-10-13</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,15 +3559,798 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>87326481</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92905</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4786</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lactifluus volemus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stjärnviksområdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>550158</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6507866</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>87326632</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stjärnviksområdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>550637</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6507701</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>87326705</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stjärnviksområdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>550346</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6507796</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>87326555</v>
+      </c>
+      <c r="B34" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stjärnviksområdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>550262</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6507807</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>87326657</v>
+      </c>
+      <c r="B35" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stjärnviksområdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>550453</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6507790</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4956560</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Butbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>550349</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6507802</v>
+      </c>
+      <c r="S36" t="n">
+        <v>100</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>1996-12-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>1996-12-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>ekskog</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>96634221</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>550355</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6507775</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX37" t="inlineStr">
         <is>
           <t>Marika Sjödin</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>87326710</v>
+      </c>
+      <c r="B38" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stjärnviksområdet, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>550346</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6507795</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2020-08-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57460-2022 artfynd.xlsx
+++ b/artfynd/A 57460-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/157786</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326642</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326539</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326482</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/182570</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326649</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326650</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326651</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326652</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326404</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/414169</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326458</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1975,6 +2040,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72231323</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740503</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740504</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2296,6 +2376,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740505</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2403,6 +2488,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326496</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326497</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,6 +2794,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326532</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2791,6 +2896,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326619</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2888,6 +2998,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326620</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2985,6 +3100,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326628</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3082,6 +3202,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326575</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3179,6 +3304,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326576</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3276,6 +3406,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326577</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3373,6 +3508,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326590</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3471,6 +3611,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326648</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3568,6 +3713,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326412</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3665,6 +3815,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326481</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3762,6 +3917,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326632</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3859,6 +4019,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326705</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3956,6 +4121,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326555</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4053,6 +4223,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326657</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4155,6 +4330,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4956560</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4254,6 +4434,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96634221</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4351,8 +4536,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87326710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>